--- a/outputs/019f6c42-2d53-7743-ab07-6293e2618dd7/price_informed_frontier_parameter_crosscheck_2026-07-17.xlsx
+++ b/outputs/019f6c42-2d53-7743-ab07-6293e2618dd7/price_informed_frontier_parameter_crosscheck_2026-07-17.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Executive Summary" sheetId="1" r:id="Recfdd14c95f5497f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Frontier Estimates" sheetId="2" r:id="Rd89c491d90884576"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="API Prices" sheetId="3" r:id="R426cca95763c42e5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Price Model" sheetId="4" r:id="Raed48a3a5abc472b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Anchors &amp; Method" sheetId="5" r:id="R13121e33e44a4a51"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sources" sheetId="6" r:id="R289b8c755ddc4fff"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Executive Summary" sheetId="1" r:id="Rbde7d0f2c0844494"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Frontier Estimates" sheetId="2" r:id="Rfa2ca45a34784281"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="API Prices" sheetId="3" r:id="Ra6e448aaf52f45f0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Price Model" sheetId="4" r:id="Rc6b7ae05df904fc9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Anchors &amp; Method" sheetId="5" r:id="Ra612150e271c473b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sources" sheetId="6" r:id="Reb1517b020414fde"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -15,7 +15,7 @@
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
 <x:comments xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:authors>
-    <x:author>tc={057713DF-9D3D-0EF1-2B49-F596FA11A139}</x:author>
+    <x:author>tc={94786C96-26A0-AAB7-EEB1-FB52B14322D4}</x:author>
   </x:authors>
   <x:commentList>
     <x:comment ref="M10" authorId="0">
@@ -35,7 +35,7 @@
 <file path=xl/comments2.xml><?xml version="1.0" encoding="utf-8"?>
 <x:comments xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:authors>
-    <x:author>tc={5DEFF58C-86AD-1CB3-D586-3F42EE9250F8}</x:author>
+    <x:author>tc={066DC467-3645-CEBE-3B2B-8C2F001610D3}</x:author>
   </x:authors>
   <x:commentList>
     <x:comment ref="B12" authorId="0">
@@ -55,7 +55,7 @@
 <file path=xl/comments3.xml><?xml version="1.0" encoding="utf-8"?>
 <x:comments xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:authors>
-    <x:author>tc={EA3413F7-F826-7DF1-0575-56C43FE8B0E2}</x:author>
+    <x:author>tc={E7A444F6-F6BF-1DFD-284B-8C925531B969}</x:author>
   </x:authors>
   <x:commentList>
     <x:comment ref="B9" authorId="0">
@@ -534,7 +534,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R9f5fbb4c3e3b4e75"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rc784055f2bb14ca7"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -545,7 +545,7 @@
 
 <file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
 <xltc:personList xmlns:xltc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments">
-  <xltc:person displayName="Codex" id="{3DB4E595-1CB0-4A6C-BB18-7636548E7F7D}"/>
+  <xltc:person displayName="Codex" id="{AD7974F1-03B3-4E94-8719-789A0E516121}"/>
 </xltc:personList>
 </file>
 
@@ -800,7 +800,7 @@
 
 <file path=xl/threadedcomments/threadedcomment.xml><?xml version="1.0" encoding="utf-8"?>
 <xltc:ThreadedComments xmlns:xltc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments">
-  <xltc:threadedComment ref="M10" dT="2026-08-01T16:02:10.52" personId="{3DB4E595-1CB0-4A6C-BB18-7636548E7F7D}" id="{057713DF-9D3D-0EF1-2B49-F596FA11A139}">
+  <xltc:threadedComment ref="M10" dT="2026-08-01T18:06:47.281" personId="{AD7974F1-03B3-4E94-8719-789A0E516121}" id="{94786C96-26A0-AAB7-EEB1-FB52B14322D4}">
     <xltc:text>Opus 4.7 and 4.8 are treated as one base. Their separate benchmark-derived priors are collapsed geometrically before pricing is applied.</xltc:text>
   </xltc:threadedComment>
 </xltc:ThreadedComments>
@@ -808,7 +808,7 @@
 
 <file path=xl/threadedcomments/threadedcomment2.xml><?xml version="1.0" encoding="utf-8"?>
 <xltc:ThreadedComments xmlns:xltc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments">
-  <xltc:threadedComment ref="B12" dT="2026-08-01T16:02:10.52" personId="{3DB4E595-1CB0-4A6C-BB18-7636548E7F7D}" id="{5DEFF58C-86AD-1CB3-D586-3F42EE9250F8}">
+  <xltc:threadedComment ref="B12" dT="2026-08-01T18:06:47.281" personId="{AD7974F1-03B3-4E94-8719-789A0E516121}" id="{066DC467-3645-CEBE-3B2B-8C2F001610D3}">
     <xltc:text>Price is capped at 15% log weight because API prices reflect product strategy, latency, tokenizer choice, and inference service design—not only physical parameter count.</xltc:text>
   </xltc:threadedComment>
 </xltc:ThreadedComments>
@@ -816,7 +816,7 @@
 
 <file path=xl/threadedcomments/threadedcomment3.xml><?xml version="1.0" encoding="utf-8"?>
 <xltc:ThreadedComments xmlns:xltc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments">
-  <xltc:threadedComment ref="B9" dT="2026-08-01T16:02:10.52" personId="{3DB4E595-1CB0-4A6C-BB18-7636548E7F7D}" id="{EA3413F7-F826-7DF1-0575-56C43FE8B0E2}">
+  <xltc:threadedComment ref="B9" dT="2026-08-01T18:06:47.281" personId="{AD7974F1-03B3-4E94-8719-789A0E516121}" id="{E7A444F6-F6BF-1DFD-284B-8C925531B969}">
     <xltc:text>The 1.5T figure is a public first-party executive disclosure of the V9 foundation scale. It is less formal than a technical report and should not be used as an active-parameter count.</xltc:text>
   </xltc:threadedComment>
 </xltc:ThreadedComments>
@@ -1408,7 +1408,7 @@
     <x:cfRule type="containsText" dxfId="1" priority="1" operator="containsText" text="anchor"/>
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R66cc9c018ed04cd9"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3678389312de495e"/>
 </x:worksheet>
 </file>
 
@@ -2252,9 +2252,9 @@
     <x:cfRule type="containsText" dxfId="0" priority="1" operator="containsText" text="anchor"/>
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8c82e8b1783a4775"/>
+  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd68523681776438f"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R66a86d50dd1845c2"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R74c05b6cea5443f2"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2702,7 +2702,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re032e5a43e3a41c3"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R795c97c30afe424b"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4106,7 +4106,7 @@
     <x:mergeCell ref="A2:O3"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb2c0ca1237434685"/>
+  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3164bfd0a9b54767"/>
 </x:worksheet>
 </file>
 
@@ -4476,7 +4476,7 @@
     <x:mergeCell ref="A28:H28"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd77837ec27e54538"/>
+  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8efd3b753011402d"/>
 </x:worksheet>
 </file>
 
@@ -4701,7 +4701,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R060d17fe8e794321"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8ee4d87adec04f49"/>
   </x:tableParts>
 </x:worksheet>
 </file>